--- a/frontend/web_ccadmin_lt/src/assets/document/excel/formats/FORMATO_CARGA_DE_STOCK.xlsx
+++ b/frontend/web_ccadmin_lt/src/assets/document/excel/formats/FORMATO_CARGA_DE_STOCK.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{67540E5F-C275-4B88-99D5-F80E47D60AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB3D04E-009A-4599-9017-F966A676651E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCTO_STOCK" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>ProductCod</t>
   </si>
@@ -43,16 +43,43 @@
     <t>NumPhysicalStock</t>
   </si>
   <si>
+    <t>NumUnitPrice</t>
+  </si>
+  <si>
+    <t>LotNumber</t>
+  </si>
+  <si>
+    <t>ExpirationDate</t>
+  </si>
+  <si>
     <t>TEXTO(20)</t>
   </si>
   <si>
     <t>NUMERO(7)</t>
   </si>
   <si>
+    <t>NUMERO</t>
+  </si>
+  <si>
+    <t>TEXTO(32)</t>
+  </si>
+  <si>
+    <t>FECHA(DD/MM/YYYY)</t>
+  </si>
+  <si>
     <t>CODIGO DE PRODUCTO</t>
   </si>
   <si>
     <t>STOCK</t>
+  </si>
+  <si>
+    <t>PRECIO UNITARIO(*)</t>
+  </si>
+  <si>
+    <t>LOTE(*)</t>
+  </si>
+  <si>
+    <t>FECHA VENCIMIENTO(*)</t>
   </si>
   <si>
     <t>StoreCod</t>
@@ -99,7 +126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,15 +149,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,74 +500,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B276"/>
+  <dimension ref="A1:E269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.5703125" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="3"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:5">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:5">
       <c r="A6" s="3"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:5">
       <c r="A7" s="3"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:5">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:5">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:5">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:5">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:5">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:5">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:5">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:5">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:5">
       <c r="A16" s="3"/>
     </row>
     <row r="17" spans="1:1">
@@ -1273,27 +1358,6 @@
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="3"/>
-    </row>
-    <row r="270" spans="1:1">
-      <c r="A270" s="3"/>
-    </row>
-    <row r="271" spans="1:1">
-      <c r="A271" s="3"/>
-    </row>
-    <row r="272" spans="1:1">
-      <c r="A272" s="3"/>
-    </row>
-    <row r="273" spans="1:1">
-      <c r="A273" s="3"/>
-    </row>
-    <row r="274" spans="1:1">
-      <c r="A274" s="3"/>
-    </row>
-    <row r="275" spans="1:1">
-      <c r="A275" s="3"/>
-    </row>
-    <row r="276" spans="1:1">
-      <c r="A276" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1310,17 +1374,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
